--- a/docs/data_collection_template.xlsx
+++ b/docs/data_collection_template.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -455,9 +455,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -528,9 +526,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -542,6 +538,23 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>then open the app &gt; Admin &gt; Refresh data now, and check the report for rejected rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Transport from big cities: add one row per route, e.g. Lahore -&gt; Islamabad, Karachi -&gt; Islamabad, Peshawar -&gt; Islamabad. The planner chains it with Islamabad -&gt; Hunza/Skardu/Gilgit automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>If a direct long-distance service exists (e.g. Lahore -&gt; Gilgit), add it as its own row; a direct row is preferred over a chained one. Many northern buses may leave from Rawalpindi, so add Rawalpindi routes if that is what you find.</t>
         </is>
       </c>
     </row>
@@ -838,13 +851,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Please choose one of the listed values." type="list">
-      <formula1>"Islamabad,Gilgit,Hunza,Skardu"</formula1>
+    <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a city from the list (add new cities in backend/database.py MAJOR_CITIES)." type="list">
+      <formula1>"Islamabad,Rawalpindi,Lahore,Karachi,Faisalabad,Multan,Peshawar,Quetta,Hyderabad,Gujranwala,Sialkot,Bahawalpur,Sargodha,Sukkur,Abbottabad,Gilgit,Hunza,Skardu"</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Please choose one of the listed values." type="list">
-      <formula1>"Islamabad,Gilgit,Hunza,Skardu"</formula1>
+    <dataValidation sqref="D3:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a city from the list (add new cities in backend/database.py MAJOR_CITIES)." type="list">
+      <formula1>"Islamabad,Rawalpindi,Lahore,Karachi,Faisalabad,Multan,Peshawar,Quetta,Hyderabad,Gujranwala,Sialkot,Bahawalpur,Sargodha,Sukkur,Abbottabad,Gilgit,Hunza,Skardu"</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Please choose one of the listed values." type="list">
+    <dataValidation sqref="I3:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Verified,Needs reconfirmation,Estimated,Unknown"</formula1>
     </dataValidation>
   </dataValidations>
